--- a/revolution-bio/redirects.xlsx
+++ b/revolution-bio/redirects.xlsx
@@ -561,12 +561,12 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>/rejusome#p-exo-boost-cream</t>
+          <t>/rejusome?p=exo-boost-cream</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>/rejusome#p-rejusome</t>
+          <t>/rejusome?p=rejusome</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>/rejusome#p-rejusome-plus</t>
+          <t>/rejusome?p=rejusome-plus</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>/rejusome#p-rejusome-plus</t>
+          <t>/rejusome?p=rejusome-plus</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>/rejusome#p-exo-boost-serum</t>
+          <t>/rejusome?p=exo-boost-serum</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>/rejusome#p-exo-boost-mask</t>
+          <t>/rejusome?p=exo-boost-mask</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>/rejusome#p-exo-boost-mist</t>
+          <t>/rejusome?p=exo-boost-mist</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -2122,12 +2122,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -2143,12 +2143,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -2164,12 +2164,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -2227,12 +2227,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -2248,12 +2248,12 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>/rejusome#p-exo-boost-cream</t>
+          <t>/rejusome?p=exo-boost-cream</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>/rejusome#p-rejusome</t>
+          <t>/rejusome?p=rejusome</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>/rejusome#p-rejusome-plus</t>
+          <t>/rejusome?p=rejusome-plus</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>/rejusome#p-rejusome-plus</t>
+          <t>/rejusome?p=rejusome-plus</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>/rejusome#p-exo-boost-serum</t>
+          <t>/rejusome?p=exo-boost-serum</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>/rejusome#p-exo-boost-mask</t>
+          <t>/rejusome?p=exo-boost-mask</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -2461,12 +2461,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -2482,12 +2482,12 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -2503,12 +2503,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -2524,12 +2524,12 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>/rejusome#p-exo-boost-mist</t>
+          <t>/rejusome?p=exo-boost-mist</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -2716,12 +2716,12 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -2812,12 +2812,12 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -2833,12 +2833,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -2854,12 +2854,12 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -2875,12 +2875,12 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -2917,12 +2917,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -2938,12 +2938,12 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -2959,12 +2959,12 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -2980,12 +2980,12 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
@@ -3043,12 +3043,12 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
@@ -3064,12 +3064,12 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
@@ -3085,12 +3085,12 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
@@ -3106,12 +3106,12 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -3148,12 +3148,12 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
@@ -3190,12 +3190,12 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
@@ -3253,12 +3253,12 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
@@ -3295,12 +3295,12 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
@@ -3316,12 +3316,12 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
@@ -3379,12 +3379,12 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
@@ -3400,12 +3400,12 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
@@ -3421,12 +3421,12 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
@@ -3442,12 +3442,12 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -3484,12 +3484,12 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
@@ -3526,12 +3526,12 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
@@ -3568,12 +3568,12 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -3631,12 +3631,12 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
@@ -3652,12 +3652,12 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -3673,12 +3673,12 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -3715,12 +3715,12 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
@@ -3736,12 +3736,12 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
@@ -3778,12 +3778,12 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
@@ -3841,12 +3841,12 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr"/>
@@ -3862,12 +3862,12 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
@@ -3883,12 +3883,12 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
@@ -4147,7 +4147,7 @@
   <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4174,14 +4174,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Сначала внесите лист «Главные 20», остальные — по желанию.</t>
+          <t>В новых адресах нет «#»: Tilda отрезает всё после #. Адрес с ?p=… сразу открывает окно нужного товара.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Редиректы заработают после переключения домена revolution.bio на Tilda.</t>
+          <t>Сначала внесите лист «Главные», остальные — по желанию.</t>
         </is>
       </c>
     </row>
